--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_47.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_47.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>IVCat</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Sessions</t>
+          <t>ExamGrade</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.1168245013658944</v>
+        <v>0.6502489750692376</v>
       </c>
       <c r="C2">
-        <v>-0.311333683610146</v>
+        <v>-0.5039632711873421</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3601889027753196</v>
+        <v>-1.114132096455639</v>
       </c>
       <c r="C3">
-        <v>1.098750865525598</v>
+        <v>0.2299338659095564</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.7933580290340601</v>
+        <v>-0.1552148049973637</v>
       </c>
       <c r="C4">
-        <v>-0.5282517567998124</v>
+        <v>0.856670056362993</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.8195894704658836</v>
+        <v>0.9318144582802373</v>
       </c>
       <c r="C5">
-        <v>0.5654417015446471</v>
+        <v>0.8090853770230853</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.066415180830582</v>
+        <v>-0.8616231524054405</v>
       </c>
       <c r="C6">
-        <v>1.629076675509377</v>
+        <v>0.1010934922109044</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.14156728110978</v>
+        <v>-0.06164575118607946</v>
       </c>
       <c r="C7">
-        <v>-0.8781921649860063</v>
+        <v>0.4887345106919</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.8845596472435482</v>
+        <v>-1.150080571933283</v>
       </c>
       <c r="C8">
-        <v>0.0005027984164142074</v>
+        <v>-0.4477144231748043</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.8185808357175545</v>
+        <v>0.7497545003105615</v>
       </c>
       <c r="C9">
-        <v>-0.1298658523235362</v>
+        <v>0.6466772017061193</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.04348510612492389</v>
+        <v>1.258307259527732</v>
       </c>
       <c r="C10">
-        <v>-0.2495863145433846</v>
+        <v>-0.4909752728618181</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.2966731415959897</v>
+        <v>1.642387226138587</v>
       </c>
       <c r="C11">
-        <v>0.4852577882492177</v>
+        <v>0.5841507867089822</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.024777808623839</v>
+        <v>0.04806611512065918</v>
       </c>
       <c r="C12">
-        <v>-1.885935380660428</v>
+        <v>-0.1969429369879437</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.3668914517253216</v>
+        <v>-0.04606140800628501</v>
       </c>
       <c r="C13">
-        <v>-1.057318576860791</v>
+        <v>-0.3641025361158782</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.2650706453368439</v>
+        <v>-0.895906377995119</v>
       </c>
       <c r="C14">
-        <v>-0.2090564780512882</v>
+        <v>-0.289913909336122</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.144713509314414</v>
+        <v>0.03935830713601569</v>
       </c>
       <c r="C15">
-        <v>1.38121109110865</v>
+        <v>-0.2612120114274058</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.01634043316640139</v>
+        <v>-0.6607891665519043</v>
       </c>
       <c r="C16">
-        <v>1.390736851991049</v>
+        <v>-1.044456961996573</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.179516180328003</v>
+        <v>0.5396977468761299</v>
       </c>
       <c r="C17">
-        <v>0.8164909757348062</v>
+        <v>-0.08183364786140696</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.9998649111118555</v>
+        <v>1.90681652272465</v>
       </c>
       <c r="C18">
-        <v>-0.7615745607231923</v>
+        <v>0.7868344265485769</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>2.309513281385398</v>
+        <v>1.816697696384315</v>
       </c>
       <c r="C19">
-        <v>-0.9354830640323381</v>
+        <v>1.753175806362204</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.008173681513128077</v>
+        <v>0.3077663489902555</v>
       </c>
       <c r="C20">
-        <v>1.857100170480166</v>
+        <v>-0.5831439031157166</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.9309382540888153</v>
+        <v>1.112290240393131</v>
       </c>
       <c r="C21">
-        <v>-0.8975687852429385</v>
+        <v>-0.3908724836330379</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.476940313371848</v>
+        <v>0.6019347437111678</v>
       </c>
       <c r="C22">
-        <v>-1.79569078501322</v>
+        <v>-0.5654303206207099</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.2561014232867478</v>
+        <v>0.3078343755604474</v>
       </c>
       <c r="C23">
-        <v>-2.035812207057495</v>
+        <v>-1.248870649658606</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.280555906040737</v>
+        <v>0.4300640417422514</v>
       </c>
       <c r="C24">
-        <v>-1.032761882089944</v>
+        <v>1.401293416539259</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.2839311288861492</v>
+        <v>-1.04922781159188</v>
       </c>
       <c r="C25">
-        <v>0.9968258036113072</v>
+        <v>-0.06007791073885937</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-1.762807632837236</v>
+        <v>-1.369089066184965</v>
       </c>
       <c r="C26">
-        <v>-2.093757155976955</v>
+        <v>-0.7964481109200052</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.8298466639357241</v>
+        <v>-0.5296802400570725</v>
       </c>
       <c r="C27">
-        <v>0.4264232572104068</v>
+        <v>-0.4793051543729956</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.7519641005835198</v>
+        <v>0.7733661752354439</v>
       </c>
       <c r="C28">
-        <v>-1.701236415376673</v>
+        <v>-0.3743237099121732</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-1.012855810087001</v>
+        <v>0.21185683047053</v>
       </c>
       <c r="C29">
-        <v>1.185785633676002</v>
+        <v>-0.1719936611294191</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.1626639331656762</v>
+        <v>-1.032834035440037</v>
       </c>
       <c r="C30">
-        <v>0.7150955273424231</v>
+        <v>0.7886083666058764</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.1009068707180014</v>
+        <v>-1.60537427161318</v>
       </c>
       <c r="C31">
-        <v>-1.361405267740347</v>
+        <v>-0.643369475209273</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.1753789010587145</v>
+        <v>0.02763716235570965</v>
       </c>
       <c r="C32">
-        <v>-1.362253157770521</v>
+        <v>0.9375485347927202</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.1631203213211969</v>
+        <v>0.001601712538420988</v>
       </c>
       <c r="C33">
-        <v>0.9327372086538259</v>
+        <v>1.092556981950802</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.5953674136699746</v>
+        <v>1.343309680363959</v>
       </c>
       <c r="C34">
-        <v>0.1327366936314477</v>
+        <v>-0.6450521054322039</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.018964773929542</v>
+        <v>1.323043828038076</v>
       </c>
       <c r="C35">
-        <v>1.215980534625321</v>
+        <v>0.2765923708294891</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.6202665202204642</v>
+        <v>0.6083345957798152</v>
       </c>
       <c r="C36">
-        <v>0.1237210107243322</v>
+        <v>1.091190237257146</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.1833800002264792</v>
+        <v>-1.73206473660638</v>
       </c>
       <c r="C37">
-        <v>-0.03541839953989558</v>
+        <v>-1.898977075479789</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>2.435851556372228</v>
+        <v>-1.7448993549993</v>
       </c>
       <c r="C38">
-        <v>-2.47016577871392</v>
+        <v>-1.091504970918447</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.4724361704381313</v>
+        <v>0.8033888994056362</v>
       </c>
       <c r="C39">
-        <v>0.4063663938628458</v>
+        <v>1.564931648766241</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.4205497269884318</v>
+        <v>1.105286801505077</v>
       </c>
       <c r="C40">
-        <v>-0.5851900408912882</v>
+        <v>0.675642674049927</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.1754134639311886</v>
+        <v>-1.257846254603842</v>
       </c>
       <c r="C41">
-        <v>0.7575565295995182</v>
+        <v>-1.646748669512328</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.539877827300853</v>
+        <v>0.5739969910878253</v>
       </c>
       <c r="C42">
-        <v>0.263542445318791</v>
+        <v>-0.1307046902367297</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>1.099108365949726</v>
+        <v>1.4808679172519</v>
       </c>
       <c r="C43">
-        <v>-0.6568250924456845</v>
+        <v>0.3350462789258972</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.3983113870611596</v>
+        <v>0.7113901635343732</v>
       </c>
       <c r="C44">
-        <v>1.327751161071656</v>
+        <v>1.02038604422558</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-2.125206404346557</v>
+        <v>-2.105110188737921</v>
       </c>
       <c r="C45">
-        <v>0.3103824702809134</v>
+        <v>0.3174932721413724</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-1.37254021070186</v>
+        <v>-0.972645706938829</v>
       </c>
       <c r="C46">
-        <v>0.6939431749343972</v>
+        <v>-1.375159603258203</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>1.020972822934336</v>
+        <v>-1.479587711939477</v>
       </c>
       <c r="C47">
-        <v>-0.5945918296711101</v>
+        <v>-0.6281215273055371</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.8387056631673045</v>
+        <v>0.2112635037162145</v>
       </c>
       <c r="C48">
-        <v>0.9106615094116952</v>
+        <v>1.219914582538346</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-1.172791983121215</v>
+        <v>2.993355656483327</v>
       </c>
       <c r="C49">
-        <v>1.556701509900124</v>
+        <v>1.494898996580137</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.3123379120484429</v>
+        <v>-0.9876330809145566</v>
       </c>
       <c r="C50">
-        <v>0.01556140254513684</v>
+        <v>-0.9479682493060992</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>-1.496976160912625</v>
+        <v>0.2946644201761913</v>
       </c>
       <c r="C51">
-        <v>0.9663330308038077</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>0.3926086556480498</v>
-      </c>
-      <c r="C52">
-        <v>-0.3421733633450462</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>-1.441662910333761</v>
-      </c>
-      <c r="C53">
-        <v>1.124509491710634</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>-0.656228740601609</v>
-      </c>
-      <c r="C54">
-        <v>1.433810861665605</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>1.686077461257606</v>
-      </c>
-      <c r="C55">
-        <v>0.3775099266866642</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>0.4586601393665628</v>
-      </c>
-      <c r="C56">
-        <v>-0.9090346788560704</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>0.5491157035173869</v>
-      </c>
-      <c r="C57">
-        <v>-0.3287589422025676</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>-1.258224528174432</v>
-      </c>
-      <c r="C58">
-        <v>-0.1111001037931162</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>-1.923864035994942</v>
-      </c>
-      <c r="C59">
-        <v>-0.09877379049495838</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>0.7797759826748611</v>
-      </c>
-      <c r="C60">
-        <v>0.3247236905662998</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>-2.733794059980807</v>
-      </c>
-      <c r="C61">
-        <v>3.474879844029331</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>0.6209339488195423</v>
-      </c>
-      <c r="C62">
-        <v>-1.229425641762718</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>-0.2350533597160784</v>
-      </c>
-      <c r="C63">
-        <v>1.559741694882979</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>0.1267046139511081</v>
-      </c>
-      <c r="C64">
-        <v>-0.2307598551883721</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>0.2514395754080921</v>
-      </c>
-      <c r="C65">
-        <v>-0.7401326607541465</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>-0.6952490648750097</v>
-      </c>
-      <c r="C66">
-        <v>-0.7884684344949682</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>0.1588576381178977</v>
-      </c>
-      <c r="C67">
-        <v>1.148048956029702</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>-0.8960203617544444</v>
-      </c>
-      <c r="C68">
-        <v>1.263758627699569</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>0.8769948721639204</v>
-      </c>
-      <c r="C69">
-        <v>-0.7962347186797092</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>0.1876356756230628</v>
-      </c>
-      <c r="C70">
-        <v>0.1372801983459186</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>-1.044930831741306</v>
-      </c>
-      <c r="C71">
-        <v>-0.9658594201138909</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>-0.1599640138475109</v>
-      </c>
-      <c r="C72">
-        <v>-0.5468443289849455</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>-0.8762344897529826</v>
-      </c>
-      <c r="C73">
-        <v>-0.06667071078876502</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>1.171116727464271</v>
-      </c>
-      <c r="C74">
-        <v>-0.9534065803136835</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>-0.0372139118490671</v>
-      </c>
-      <c r="C75">
-        <v>1.330277362628234</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>1.050951319596599</v>
-      </c>
-      <c r="C76">
-        <v>-1.554957827052653</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>-0.7611703495408755</v>
-      </c>
-      <c r="C77">
-        <v>-1.383638327818207</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>-2.093834058827603</v>
-      </c>
-      <c r="C78">
-        <v>-0.5662902694985766</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>0.8348137097280626</v>
-      </c>
-      <c r="C79">
-        <v>-0.675958293146562</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>0.03710772295949777</v>
-      </c>
-      <c r="C80">
-        <v>0.6602278601787633</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>0.3044578365151854</v>
-      </c>
-      <c r="C81">
-        <v>-0.01726035998017045</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>0.3779799754970775</v>
-      </c>
-      <c r="C82">
-        <v>0.08253304651615573</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>-0.2775647116179622</v>
-      </c>
-      <c r="C83">
-        <v>-0.9298690140154556</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>0.1219445388592668</v>
-      </c>
-      <c r="C84">
-        <v>-0.3287166886433471</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-2.341250464547115</v>
-      </c>
-      <c r="C85">
-        <v>0.7398965919517628</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>1.424006449598371</v>
-      </c>
-      <c r="C86">
-        <v>-1.240571169239524</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>0.5697836539147084</v>
-      </c>
-      <c r="C87">
-        <v>-0.666829376075764</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>-0.6078933641743005</v>
-      </c>
-      <c r="C88">
-        <v>-2.326912847485539</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>0.1228032465460302</v>
-      </c>
-      <c r="C89">
-        <v>-0.05892099084527301</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>-1.989661262420574</v>
-      </c>
-      <c r="C90">
-        <v>-0.5383806957668926</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>-0.4019399578914211</v>
-      </c>
-      <c r="C91">
-        <v>-0.4424585583870985</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>0.6182761629263029</v>
-      </c>
-      <c r="C92">
-        <v>0.82131027827634</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>-0.3373502121992047</v>
-      </c>
-      <c r="C93">
-        <v>1.974885192205787</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>-0.2228718295669697</v>
-      </c>
-      <c r="C94">
-        <v>-0.5006914441722188</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>0.0006413565859196077</v>
-      </c>
-      <c r="C95">
-        <v>0.264344062829828</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>-0.3413355741481393</v>
-      </c>
-      <c r="C96">
-        <v>1.789478704086888</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>0.2955204831491665</v>
-      </c>
-      <c r="C97">
-        <v>0.603712849799948</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>0.5943009313257014</v>
-      </c>
-      <c r="C98">
-        <v>-0.2048961638292015</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>-0.2311661096887528</v>
-      </c>
-      <c r="C99">
-        <v>-0.8035522481911093</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>0.08518983417018404</v>
-      </c>
-      <c r="C100">
-        <v>0.7480656606993201</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>-2.50657506828927</v>
-      </c>
-      <c r="C101">
-        <v>0.9326610851442827</v>
+        <v>0.4417626616124423</v>
       </c>
     </row>
   </sheetData>
